--- a/jogos_2024-09-06.xlsx
+++ b/jogos_2024-09-06.xlsx
@@ -1159,19 +1159,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1185,55 +1185,55 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M6" t="n">
         <v>3.2</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O6" t="n">
         <v>3.4</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2</v>
-      </c>
-      <c r="O6" t="n">
-        <v>4</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="T6" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V6" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="W6" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="X6" t="n">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.62</v>
+        <v>4.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" t="n">
         <v>1.85</v>
@@ -1243,25 +1243,25 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>['48']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.51</v>
+        <v>1.26</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.38</v>
+        <v>1.69</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45541.5625</v>
@@ -1288,109 +1288,109 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N7" t="n">
         <v>2</v>
       </c>
-      <c r="H7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>4</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.5</v>
       </c>
       <c r="P7" t="n">
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="R7" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="S7" t="n">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="T7" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U7" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="V7" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W7" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="X7" t="n">
-        <v>2.87</v>
+        <v>2.72</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.28</v>
+        <v>4.62</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['1', '44']</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['50', '62', '87']</t>
+          <t>['48']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.19</v>
+        <v>1.51</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.8</v>
+        <v>1.38</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.57</v>
+        <v>2.6</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45541.5625</v>
@@ -1417,25 +1417,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nîmes</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,55 +1443,55 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="O8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T8" t="n">
         <v>2.88</v>
       </c>
-      <c r="P8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.05</v>
-      </c>
       <c r="U8" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="V8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="X8" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AC8" t="n">
         <v>1.85</v>
@@ -1501,25 +1501,25 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['36', '90']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['13', '50']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45541.5625</v>
@@ -1675,25 +1675,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>3.8</v>
+        <v>1.95</v>
       </c>
       <c r="O10" t="n">
-        <v>2.6</v>
+        <v>4.33</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.33</v>
+        <v>2.75</v>
       </c>
       <c r="R10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W10" t="n">
         <v>1.37</v>
       </c>
-      <c r="S10" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.29</v>
-      </c>
       <c r="X10" t="n">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="Y10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC10" t="n">
         <v>2.1</v>
       </c>
-      <c r="Z10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AD10" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['32', '48', '90+1']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4', '22', '40']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.57</v>
+        <v>2.75</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.75</v>
+        <v>1.67</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45541.5625</v>
@@ -1804,22 +1804,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1830,43 +1830,43 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.45</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="P11" t="n">
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W11" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="X11" t="n">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="Y11" t="n">
         <v>2.25</v>
@@ -1875,38 +1875,38 @@
         <v>1.62</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.2</v>
+        <v>4.28</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1', '44']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['50', '62', '87']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.91</v>
+        <v>3</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45541.5625</v>
@@ -2062,109 +2062,109 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Nîmes</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M13" t="n">
         <v>3</v>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="M13" t="n">
-        <v>3.1</v>
-      </c>
       <c r="N13" t="n">
-        <v>1.95</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
-        <v>4.33</v>
+        <v>2.88</v>
       </c>
       <c r="P13" t="n">
         <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="T13" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="V13" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W13" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="X13" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['32', '48', '90+1']</t>
+          <t>['36', '90']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['4', '22', '40']</t>
+          <t>['13', '50']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.75</v>
+        <v>1.73</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45541.5625</v>
@@ -2578,16 +2578,16 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>1</v>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="O17" t="n">
+        <v>4</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="Y17" t="n">
         <v>2.25</v>
       </c>
-      <c r="P17" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.8</v>
-      </c>
       <c r="Z17" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.88</v>
+        <v>3.74</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['90+11']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['58']</t>
+          <t>['68']</t>
         </is>
       </c>
       <c r="AG17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.17</v>
       </c>
-      <c r="AH17" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AI17" t="n">
-        <v>1.57</v>
+        <v>2.52</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.7</v>
+        <v>1.71</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45541.65625</v>
@@ -2707,109 +2707,109 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
         <v>2</v>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>3.77</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="R18" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>2.55</v>
+        <v>3.04</v>
       </c>
       <c r="T18" t="n">
-        <v>3.14</v>
+        <v>2.58</v>
       </c>
       <c r="U18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['50']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>['38', '73']</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.33</v>
       </c>
-      <c r="V18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>['68']</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AI18" t="n">
-        <v>2.52</v>
+        <v>2.26</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45541.65625</v>
@@ -2965,19 +2965,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="M20" t="n">
         <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="O20" t="n">
-        <v>4.65</v>
+        <v>2.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.17</v>
+        <v>4.94</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="T20" t="n">
-        <v>2.38</v>
+        <v>2.68</v>
       </c>
       <c r="U20" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="V20" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>['90+11']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>['58']</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
         <v>1.17</v>
       </c>
-      <c r="X20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>['67']</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.16</v>
+        <v>1.85</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.65</v>
+        <v>1.57</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45541.65625</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O21" t="n">
         <v>3.25</v>
       </c>
-      <c r="M21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3.77</v>
-      </c>
       <c r="P21" t="n">
-        <v>2.33</v>
+        <v>1.91</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.66</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="S21" t="n">
-        <v>3.04</v>
+        <v>2.38</v>
       </c>
       <c r="T21" t="n">
-        <v>2.58</v>
+        <v>3.45</v>
       </c>
       <c r="U21" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W21" t="n">
-        <v>1.21</v>
+        <v>1.45</v>
       </c>
       <c r="X21" t="n">
-        <v>3.74</v>
+        <v>2.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.65</v>
+        <v>2.6</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.1</v>
+        <v>1.48</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.67</v>
+        <v>4.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.59</v>
+        <v>2.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['50']</t>
+          <t>['83']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['38', '73']</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.26</v>
+        <v>1.83</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.74</v>
+        <v>2.38</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45541.65625</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,19 +3223,19 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="O22" t="n">
-        <v>3.25</v>
+        <v>4.65</v>
       </c>
       <c r="P22" t="n">
-        <v>1.91</v>
+        <v>2.28</v>
       </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>2.17</v>
       </c>
       <c r="R22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U22" t="n">
         <v>1.53</v>
       </c>
-      <c r="S22" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.25</v>
-      </c>
       <c r="V22" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="W22" t="n">
-        <v>1.45</v>
+        <v>1.17</v>
       </c>
       <c r="X22" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.6</v>
+        <v>1.73</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.48</v>
+        <v>2</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['83']</t>
+          <t>['67']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['59']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.45</v>
+        <v>2.1</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.45</v>
+        <v>1.16</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.83</v>
+        <v>2.65</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.38</v>
+        <v>1.5</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45541.65625</v>
